--- a/exports/AMBUJACEM_full_report.xlsx
+++ b/exports/AMBUJACEM_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q62"/>
+  <dimension ref="A1:U62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>4.75</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44579.38541666666</v>
+        <v>44579.55208333334</v>
       </c>
       <c r="H2" t="n">
-        <v>394.6</v>
+        <v>380</v>
       </c>
       <c r="I2" t="n">
         <v>384.9831560350765</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.16</v>
+        <v>-4.82</v>
       </c>
       <c r="L2" t="n">
-        <v>2.04</v>
+        <v>5.06</v>
       </c>
       <c r="M2" t="n">
         <v>0.49</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>8.68</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44592.55208333334</v>
+        <v>44593.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>365</v>
+        <v>373.85</v>
       </c>
       <c r="I3" t="n">
         <v>371.7799741000994</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K3" t="n">
-        <v>3.95</v>
+        <v>1.62</v>
       </c>
       <c r="L3" t="n">
         <v>3.93</v>
       </c>
       <c r="M3" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="N3" t="n">
-        <v>2.33</v>
+        <v>4.73</v>
       </c>
       <c r="O3" t="n">
         <v>-6.75</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>7.19</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44606.38541666666</v>
+        <v>44606.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>360.8</v>
+        <v>355</v>
       </c>
       <c r="I4" t="n">
         <v>360.6254333535137</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K4" t="n">
-        <v>-3.49</v>
+        <v>-5.04</v>
       </c>
       <c r="L4" t="n">
-        <v>4.13</v>
+        <v>5.3</v>
       </c>
       <c r="M4" t="n">
         <v>1.43</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>6.56</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44636.38541666666</v>
+        <v>44636.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>303.15</v>
+        <v>309.7</v>
       </c>
       <c r="I5" t="n">
         <v>304.0423898393656</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>29.83333333333333</v>
+        <v>30</v>
       </c>
       <c r="K5" t="n">
-        <v>14.61</v>
+        <v>12.76</v>
       </c>
       <c r="L5" t="n">
         <v>3.62</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>7.98</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44691.38541666666</v>
+        <v>44691.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>366.05</v>
+        <v>356</v>
       </c>
       <c r="I6" t="n">
         <v>356.6478644626345</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>54.83333333333334</v>
+        <v>55</v>
       </c>
       <c r="K6" t="n">
-        <v>18.2</v>
+        <v>14.95</v>
       </c>
       <c r="L6" t="n">
         <v>6.85</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>8.5</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44739.55208333334</v>
+        <v>44740.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>365.25</v>
+        <v>366.15</v>
       </c>
       <c r="I7" t="n">
         <v>366.1231167951084</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>48</v>
+        <v>48.83333333333334</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.6</v>
+        <v>-2.85</v>
       </c>
       <c r="L7" t="n">
         <v>7.29</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>2.57</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44798.38541666666</v>
+        <v>44798.55208333334</v>
       </c>
       <c r="H8" t="n">
-        <v>399.95</v>
+        <v>396.85</v>
       </c>
       <c r="I8" t="n">
         <v>399.777949075228</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>58</v>
+        <v>58.16666666666666</v>
       </c>
       <c r="K8" t="n">
-        <v>9.23</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="L8" t="n">
         <v>1.11</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>6.19</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44810.38541666666</v>
+        <v>44810.55208333334</v>
       </c>
       <c r="H9" t="n">
-        <v>419.2</v>
+        <v>441</v>
       </c>
       <c r="I9" t="n">
         <v>421.4174221895645</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>11.83333333333333</v>
+        <v>12</v>
       </c>
       <c r="K9" t="n">
-        <v>-5.63</v>
+        <v>-11.13</v>
       </c>
       <c r="L9" t="n">
-        <v>6.98</v>
+        <v>11.13</v>
       </c>
       <c r="M9" t="n">
         <v>0.79</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>8.119999999999999</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44830.38541666666</v>
+        <v>44830.55208333334</v>
       </c>
       <c r="H10" t="n">
-        <v>533.05</v>
+        <v>501.1</v>
       </c>
       <c r="I10" t="n">
         <v>514.3281521691537</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>19.83333333333333</v>
+        <v>20</v>
       </c>
       <c r="K10" t="n">
-        <v>20.87</v>
+        <v>13.63</v>
       </c>
       <c r="L10" t="n">
         <v>5.02</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>16.85</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44868.55208333334</v>
+        <v>44869.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>539.2</v>
+        <v>553</v>
       </c>
       <c r="I11" t="n">
         <v>546.5871379271206</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>38</v>
+        <v>38.83333333333334</v>
       </c>
       <c r="K11" t="n">
-        <v>-7.6</v>
+        <v>-10.36</v>
       </c>
       <c r="L11" t="n">
-        <v>9.56</v>
+        <v>10.86</v>
       </c>
       <c r="M11" t="n">
         <v>2.95</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>6.65</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44910.38541666666</v>
+        <v>44910.55208333334</v>
       </c>
       <c r="H12" t="n">
-        <v>572.1</v>
+        <v>559</v>
       </c>
       <c r="I12" t="n">
         <v>561.4393907566717</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>41</v>
+        <v>41.16666666666666</v>
       </c>
       <c r="K12" t="n">
-        <v>3.45</v>
+        <v>1.08</v>
       </c>
       <c r="L12" t="n">
         <v>2.56</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>6.14</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44986.55208333334</v>
+        <v>44987.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>354.5</v>
+        <v>365</v>
       </c>
       <c r="I13" t="n">
         <v>364.0903513360365</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>76</v>
+        <v>76.83333333333333</v>
       </c>
       <c r="K13" t="n">
-        <v>36.58</v>
+        <v>34.7</v>
       </c>
       <c r="L13" t="n">
         <v>2.5</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>105</v>
+        <v>106</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>4</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>12.63</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>45098.55208333334</v>
+        <v>45099.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>450.7</v>
+        <v>443.2</v>
       </c>
       <c r="I14" t="n">
         <v>446.0729019122649</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>111.1666666666667</v>
+        <v>112</v>
       </c>
       <c r="K14" t="n">
-        <v>23.48</v>
+        <v>21.42</v>
       </c>
       <c r="L14" t="n">
         <v>6.63</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>148</v>
+        <v>149</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>5.57</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45131.55208333334</v>
+        <v>45132.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>423.2</v>
+        <v>433.85</v>
       </c>
       <c r="I15" t="n">
         <v>431.6160877860781</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>33</v>
       </c>
       <c r="K15" t="n">
-        <v>4.51</v>
+        <v>2.11</v>
       </c>
       <c r="L15" t="n">
         <v>2.2</v>
@@ -1296,7 +1475,7 @@
         <v>0.45</v>
       </c>
       <c r="N15" t="n">
-        <v>2.3</v>
+        <v>4.32</v>
       </c>
       <c r="O15" t="n">
         <v>-1.18</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>5.23</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45149.55208333334</v>
+        <v>45152.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>455.3</v>
+        <v>439.9</v>
       </c>
       <c r="I16" t="n">
         <v>444.0601888933127</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K16" t="n">
-        <v>4.94</v>
+        <v>1.39</v>
       </c>
       <c r="L16" t="n">
         <v>2.47</v>
       </c>
       <c r="M16" t="n">
-        <v>0.04</v>
+        <v>1.04</v>
       </c>
       <c r="N16" t="n">
-        <v>2.01</v>
+        <v>3.36</v>
       </c>
       <c r="O16" t="n">
         <v>4.32</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>7.55</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45159.38541666666</v>
+        <v>45159.55208333334</v>
       </c>
       <c r="H17" t="n">
-        <v>459</v>
+        <v>467.4</v>
       </c>
       <c r="I17" t="n">
         <v>462.6655312244836</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K17" t="n">
-        <v>-4.34</v>
+        <v>-6.25</v>
       </c>
       <c r="L17" t="n">
-        <v>4.79</v>
+        <v>6.62</v>
       </c>
       <c r="M17" t="n">
         <v>0.46</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>7.12</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45163.38541666666</v>
+        <v>45163.55208333334</v>
       </c>
       <c r="H18" t="n">
-        <v>438.15</v>
+        <v>433.8</v>
       </c>
       <c r="I18" t="n">
         <v>437.7547049659763</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>3.833333333333333</v>
+        <v>4</v>
       </c>
       <c r="K18" t="n">
-        <v>-6.26</v>
+        <v>-7.19</v>
       </c>
       <c r="L18" t="n">
         <v>7.98</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>7.92</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45209.55208333334</v>
+        <v>45210.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>435</v>
+        <v>443.75</v>
       </c>
       <c r="I19" t="n">
         <v>438.8411589168215</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>46</v>
+        <v>46.83333333333334</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.28</v>
+        <v>-2.29</v>
       </c>
       <c r="L19" t="n">
         <v>4.63</v>
@@ -1524,7 +1751,7 @@
         <v>1.24</v>
       </c>
       <c r="N19" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="O19" t="n">
         <v>-3.39</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>4.89</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45219.55208333334</v>
+        <v>45222.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>430</v>
+        <v>421.05</v>
       </c>
       <c r="I20" t="n">
         <v>427.570529405126</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K20" t="n">
-        <v>-3.1</v>
+        <v>-5.12</v>
       </c>
       <c r="L20" t="n">
-        <v>3.53</v>
+        <v>5.12</v>
       </c>
       <c r="M20" t="n">
         <v>0.35</v>
       </c>
       <c r="N20" t="n">
-        <v>1.95</v>
+        <v>3.83</v>
       </c>
       <c r="O20" t="n">
         <v>2.75</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>6.36</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45254.55208333334</v>
+        <v>45258.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>415.2</v>
+        <v>432.3</v>
       </c>
       <c r="I21" t="n">
         <v>427.5622713523721</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K21" t="n">
-        <v>1.39</v>
+        <v>-2.67</v>
       </c>
       <c r="L21" t="n">
-        <v>2.78</v>
+        <v>3.42</v>
       </c>
       <c r="M21" t="n">
-        <v>1.11</v>
+        <v>1.4</v>
       </c>
       <c r="N21" t="n">
-        <v>3.2</v>
+        <v>3.81</v>
       </c>
       <c r="O21" t="n">
         <v>-3.83</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>5.6</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45280.38541666666</v>
+        <v>45280.55208333334</v>
       </c>
       <c r="H22" t="n">
-        <v>503.65</v>
+        <v>488.4</v>
       </c>
       <c r="I22" t="n">
         <v>496.1007115703933</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>22</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="K22" t="n">
-        <v>16.5</v>
+        <v>12.98</v>
       </c>
       <c r="L22" t="n">
         <v>3.48</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>8.76</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45289.55208333334</v>
+        <v>45292.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>519.7</v>
+        <v>534.2</v>
       </c>
       <c r="I23" t="n">
         <v>529.3443817423185</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>9</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K23" t="n">
-        <v>-6.41</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>7.08</v>
+        <v>10.15</v>
       </c>
       <c r="M23" t="n">
         <v>2.55</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>6.65</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45363.55208333334</v>
+        <v>45364.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>585.2</v>
+        <v>569.3</v>
       </c>
       <c r="I24" t="n">
         <v>583.9003406830823</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>71.16666666666667</v>
+        <v>72</v>
       </c>
       <c r="K24" t="n">
-        <v>9.550000000000001</v>
+        <v>6.57</v>
       </c>
       <c r="L24" t="n">
         <v>4.72</v>
@@ -1809,7 +2096,7 @@
         <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>3.33</v>
+        <v>4.48</v>
       </c>
       <c r="O24" t="n">
         <v>2.02</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>99</v>
+        <v>100</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,25 +2144,25 @@
         <v>7.65</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45377.55208333334</v>
+        <v>45378.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>593.1</v>
+        <v>606</v>
       </c>
       <c r="I25" t="n">
         <v>601.9383861675958</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K25" t="n">
-        <v>-4.18</v>
+        <v>-6.45</v>
       </c>
       <c r="L25" t="n">
-        <v>6.07</v>
+        <v>7.15</v>
       </c>
       <c r="M25" t="n">
-        <v>0.71</v>
+        <v>0.83</v>
       </c>
       <c r="N25" t="n">
         <v>4.47</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>6.48</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45415.55208333334</v>
+        <v>45418.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>621.1</v>
+        <v>611.4</v>
       </c>
       <c r="I26" t="n">
         <v>611.8516366411895</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>37.16666666666666</v>
+        <v>40</v>
       </c>
       <c r="K26" t="n">
-        <v>2.49</v>
+        <v>0.89</v>
       </c>
       <c r="L26" t="n">
         <v>2.07</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>6.51</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45428.55208333334</v>
+        <v>45429.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>615</v>
+        <v>615.8</v>
       </c>
       <c r="I27" t="n">
         <v>615.4745605904841</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.59</v>
+        <v>-0.72</v>
       </c>
       <c r="L27" t="n">
         <v>2.35</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>5.74</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>674</v>
+        <v>569</v>
       </c>
       <c r="I28" t="n">
         <v>632.0033591418238</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K28" t="n">
-        <v>9.449999999999999</v>
+        <v>-7.6</v>
       </c>
       <c r="L28" t="n">
-        <v>0.76</v>
+        <v>15.82</v>
       </c>
       <c r="M28" t="n">
-        <v>0.37</v>
+        <v>0.47</v>
       </c>
       <c r="N28" t="n">
-        <v>1.32</v>
+        <v>16.64</v>
       </c>
       <c r="O28" t="n">
         <v>0.86</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>19.1</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45455.38541666666</v>
+        <v>45455.55208333334</v>
       </c>
       <c r="H29" t="n">
-        <v>647.45</v>
+        <v>667.9</v>
       </c>
       <c r="I29" t="n">
         <v>657.8365290951227</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K29" t="n">
-        <v>-13.79</v>
+        <v>-17.38</v>
       </c>
       <c r="L29" t="n">
-        <v>17.92</v>
+        <v>18.76</v>
       </c>
       <c r="M29" t="n">
         <v>2.34</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>9.630000000000001</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45504.55208333334</v>
+        <v>45505.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>681.25</v>
+        <v>656.65</v>
       </c>
       <c r="I30" t="n">
         <v>656.7690245838222</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>49</v>
+        <v>49.83333333333334</v>
       </c>
       <c r="K30" t="n">
-        <v>2</v>
+        <v>-1.68</v>
       </c>
       <c r="L30" t="n">
         <v>3.69</v>
@@ -2151,7 +2510,7 @@
         <v>0.97</v>
       </c>
       <c r="N30" t="n">
-        <v>1.87</v>
+        <v>2.39</v>
       </c>
       <c r="O30" t="n">
         <v>4.2</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>7.4</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45562.55208333334</v>
+        <v>45565.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>632</v>
+        <v>641.2</v>
       </c>
       <c r="I31" t="n">
         <v>632.4657495438457</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>57.16666666666666</v>
+        <v>60</v>
       </c>
       <c r="K31" t="n">
-        <v>3.75</v>
+        <v>2.35</v>
       </c>
       <c r="L31" t="n">
         <v>3.71</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>4.87</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45569.55208333334</v>
+        <v>45572.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>611.6</v>
+        <v>594.35</v>
       </c>
       <c r="I32" t="n">
         <v>609.9909869598906</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K32" t="n">
-        <v>-4.62</v>
+        <v>-7.31</v>
       </c>
       <c r="L32" t="n">
-        <v>5.71</v>
+        <v>8.34</v>
       </c>
       <c r="M32" t="n">
         <v>1.63</v>
       </c>
       <c r="N32" t="n">
-        <v>2.57</v>
+        <v>3.44</v>
       </c>
       <c r="O32" t="n">
         <v>-0.32</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>7.57</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45625.38541666666</v>
+        <v>45625.55208333334</v>
       </c>
       <c r="H33" t="n">
-        <v>526.3</v>
+        <v>532</v>
       </c>
       <c r="I33" t="n">
         <v>529.795813192621</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>53</v>
+        <v>53.16666666666666</v>
       </c>
       <c r="K33" t="n">
-        <v>11.45</v>
+        <v>10.49</v>
       </c>
       <c r="L33" t="n">
         <v>4.21</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>8.630000000000001</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45646.38541666666</v>
+        <v>45646.55208333334</v>
       </c>
       <c r="H34" t="n">
-        <v>560.55</v>
+        <v>550.85</v>
       </c>
       <c r="I34" t="n">
         <v>552.3601917317623</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>20.83333333333333</v>
+        <v>21</v>
       </c>
       <c r="K34" t="n">
-        <v>5.37</v>
+        <v>3.54</v>
       </c>
       <c r="L34" t="n">
         <v>1.11</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,25 +2834,25 @@
         <v>5.65</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45672.55208333334</v>
+        <v>45673.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>519</v>
+        <v>539.05</v>
       </c>
       <c r="I35" t="n">
         <v>530.5374772963297</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>26</v>
+        <v>26.83333333333333</v>
       </c>
       <c r="K35" t="n">
-        <v>5.78</v>
+        <v>2.14</v>
       </c>
       <c r="L35" t="n">
         <v>2.21</v>
       </c>
       <c r="M35" t="n">
-        <v>0.92</v>
+        <v>2.89</v>
       </c>
       <c r="N35" t="n">
         <v>4.91</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,22 +2903,22 @@
         <v>7.41</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45686.55208333334</v>
+        <v>45687.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>521.9</v>
+        <v>501.25</v>
       </c>
       <c r="I36" t="n">
         <v>520.8492978292064</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K36" t="n">
-        <v>-3.18</v>
+        <v>-7.01</v>
       </c>
       <c r="L36" t="n">
-        <v>3.91</v>
+        <v>7.78</v>
       </c>
       <c r="M36" t="n">
         <v>0.73</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>12.32</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45721.55208333334</v>
+        <v>45722.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>489.6</v>
+        <v>496.9</v>
       </c>
       <c r="I37" t="n">
         <v>492.1348068889003</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K37" t="n">
-        <v>2.32</v>
+        <v>0.87</v>
       </c>
       <c r="L37" t="n">
         <v>5.4</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>6.98</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45771.55208333334</v>
+        <v>45772.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>572</v>
+        <v>548.15</v>
       </c>
       <c r="I38" t="n">
         <v>552.3654004305175</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>49.16666666666666</v>
+        <v>50</v>
       </c>
       <c r="K38" t="n">
-        <v>15.11</v>
+        <v>10.31</v>
       </c>
       <c r="L38" t="n">
         <v>3.38</v>
@@ -2607,7 +3062,7 @@
         <v>6.4</v>
       </c>
       <c r="N38" t="n">
-        <v>2.27</v>
+        <v>4.2</v>
       </c>
       <c r="O38" t="n">
         <v>1.31</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>7.99</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45792.55208333334</v>
+        <v>45793.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>548</v>
+        <v>563.65</v>
       </c>
       <c r="I39" t="n">
         <v>551.4149229918552</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K39" t="n">
-        <v>0.03</v>
+        <v>-2.83</v>
       </c>
       <c r="L39" t="n">
         <v>4.75</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>6.23</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45820.38541666666</v>
+        <v>45820.55208333334</v>
       </c>
       <c r="H40" t="n">
-        <v>558.15</v>
+        <v>547</v>
       </c>
       <c r="I40" t="n">
         <v>548.9284664384149</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>27</v>
+        <v>27.16666666666667</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.98</v>
+        <v>-2.95</v>
       </c>
       <c r="L40" t="n">
-        <v>2.93</v>
+        <v>3.29</v>
       </c>
       <c r="M40" t="n">
         <v>0.5</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>5.06</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45831.55208333334</v>
+        <v>45832.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>534.75</v>
+        <v>558.65</v>
       </c>
       <c r="I41" t="n">
         <v>554.6224114516507</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>11</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K41" t="n">
-        <v>2.24</v>
+        <v>-2.13</v>
       </c>
       <c r="L41" t="n">
-        <v>2.18</v>
+        <v>2.89</v>
       </c>
       <c r="M41" t="n">
-        <v>0.7</v>
+        <v>0.79</v>
       </c>
       <c r="N41" t="n">
-        <v>1.21</v>
+        <v>4.16</v>
       </c>
       <c r="O41" t="n">
         <v>-2.67</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>6.46</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45869.38541666666</v>
+        <v>45869.55208333334</v>
       </c>
       <c r="H42" t="n">
-        <v>619.85</v>
+        <v>589.9</v>
       </c>
       <c r="I42" t="n">
         <v>600.702837357366</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>37</v>
+        <v>37.16666666666666</v>
       </c>
       <c r="K42" t="n">
-        <v>10.95</v>
+        <v>5.59</v>
       </c>
       <c r="L42" t="n">
         <v>3.52</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>8.390000000000001</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45917.38541666666</v>
+        <v>45917.55208333334</v>
       </c>
       <c r="H43" t="n">
-        <v>580.85</v>
+        <v>582.6</v>
       </c>
       <c r="I43" t="n">
         <v>581.0887972556486</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>47.83333333333334</v>
+        <v>48</v>
       </c>
       <c r="K43" t="n">
-        <v>1.53</v>
+        <v>1.24</v>
       </c>
       <c r="L43" t="n">
         <v>5.92</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>4.3</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45926.38541666666</v>
+        <v>45926.55208333334</v>
       </c>
       <c r="H44" t="n">
-        <v>568.9</v>
+        <v>565.35</v>
       </c>
       <c r="I44" t="n">
         <v>568.643563866066</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>8.833333333333334</v>
+        <v>9</v>
       </c>
       <c r="K44" t="n">
-        <v>-2.35</v>
+        <v>-2.96</v>
       </c>
       <c r="L44" t="n">
-        <v>2.5</v>
+        <v>3.18</v>
       </c>
       <c r="M44" t="n">
         <v>0.03</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>5.17</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45961.55208333334</v>
+        <v>45964.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>565.8</v>
+        <v>575.55</v>
       </c>
       <c r="I45" t="n">
         <v>573.0343955425648</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>35</v>
+        <v>37.83333333333334</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.08</v>
+        <v>-1.8</v>
       </c>
       <c r="L45" t="n">
         <v>2.58</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,25 +3593,25 @@
         <v>4.48</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45981.55208333334</v>
+        <v>45982.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>556.4</v>
+        <v>550.3</v>
       </c>
       <c r="I46" t="n">
         <v>554.6238486629726</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K46" t="n">
-        <v>-3.33</v>
+        <v>-4.39</v>
       </c>
       <c r="L46" t="n">
-        <v>4.34</v>
+        <v>5.31</v>
       </c>
       <c r="M46" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="N46" t="n">
         <v>2.03</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>3.67</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>46003.55208333334</v>
+        <v>46006.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>546.25</v>
+        <v>553.9</v>
       </c>
       <c r="I47" t="n">
         <v>546.8060772314677</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K47" t="n">
-        <v>0.74</v>
+        <v>-0.65</v>
       </c>
       <c r="L47" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="M47" t="n">
         <v>0.63</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>4.76</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>46029.55208333334</v>
+        <v>46030.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>561.5</v>
+        <v>550.05</v>
       </c>
       <c r="I48" t="n">
         <v>554.1604834929822</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K48" t="n">
-        <v>1.37</v>
+        <v>-0.7</v>
       </c>
       <c r="L48" t="n">
         <v>3.48</v>
@@ -3177,7 +3752,7 @@
         <v>0.33</v>
       </c>
       <c r="N48" t="n">
-        <v>1.43</v>
+        <v>2.76</v>
       </c>
       <c r="O48" t="n">
         <v>1.42</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,25 +3800,25 @@
         <v>4.26</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>46036.55208333334</v>
+        <v>46038.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>549.2</v>
+        <v>552.8</v>
       </c>
       <c r="I49" t="n">
         <v>552.2213483658725</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K49" t="n">
-        <v>0.15</v>
+        <v>-0.5</v>
       </c>
       <c r="L49" t="n">
         <v>2.17</v>
       </c>
       <c r="M49" t="n">
-        <v>0.13</v>
+        <v>0.42</v>
       </c>
       <c r="N49" t="n">
         <v>2.27</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>4.43</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>46044.55208333334</v>
+        <v>46045.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>547</v>
+        <v>527.75</v>
       </c>
       <c r="I50" t="n">
         <v>530.0578220402832</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K50" t="n">
-        <v>-1.05</v>
+        <v>-4.53</v>
       </c>
       <c r="L50" t="n">
-        <v>3.91</v>
+        <v>4.6</v>
       </c>
       <c r="M50" t="n">
         <v>0.47</v>
       </c>
       <c r="N50" t="n">
-        <v>2.68</v>
+        <v>5.05</v>
       </c>
       <c r="O50" t="n">
         <v>0.63</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>7.2</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46059.55208333334</v>
+        <v>46062.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>529</v>
+        <v>541.9</v>
       </c>
       <c r="I51" t="n">
         <v>539.7778343601047</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.24</v>
+        <v>-2.68</v>
       </c>
       <c r="L51" t="n">
         <v>3.93</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>7.03</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46073.55208333334</v>
+        <v>46076.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>513.75</v>
+        <v>512.3</v>
       </c>
       <c r="I52" t="n">
         <v>512.5885805631436</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K52" t="n">
-        <v>-5.19</v>
+        <v>-5.46</v>
       </c>
       <c r="L52" t="n">
         <v>6.14</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>4.96</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46118.38541666666</v>
+        <v>46118.55208333334</v>
       </c>
       <c r="H53" t="n">
-        <v>422.4</v>
+        <v>430</v>
       </c>
       <c r="I53" t="n">
         <v>429.6165146726508</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>42</v>
+        <v>42.16666666666666</v>
       </c>
       <c r="K53" t="n">
-        <v>17.55</v>
+        <v>16.06</v>
       </c>
       <c r="L53" t="n">
         <v>1.24</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>8.140000000000001</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46146.55208333334</v>
+        <v>46147.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>444.6</v>
+        <v>435.1</v>
       </c>
       <c r="I54" t="n">
         <v>435.9029163502139</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>28</v>
+        <v>28.83333333333333</v>
       </c>
       <c r="K54" t="n">
-        <v>3.4</v>
+        <v>1.19</v>
       </c>
       <c r="L54" t="n">
         <v>2.79</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>8.220000000000001</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46168.55208333334</v>
+        <v>46169.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>450.4</v>
+        <v>456.8</v>
       </c>
       <c r="I55" t="n">
         <v>452.4842946782802</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K55" t="n">
-        <v>-3.52</v>
+        <v>-4.99</v>
       </c>
       <c r="L55" t="n">
-        <v>5.25</v>
+        <v>6.18</v>
       </c>
       <c r="M55" t="n">
         <v>1.07</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>5.42</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46174.38541666666</v>
+        <v>46174.55208333334</v>
       </c>
       <c r="H56" t="n">
-        <v>440.95</v>
+        <v>434.95</v>
       </c>
       <c r="I56" t="n">
         <v>435.4455476885237</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>5</v>
+        <v>5.166666666666667</v>
       </c>
       <c r="K56" t="n">
-        <v>-3.47</v>
+        <v>-4.78</v>
       </c>
       <c r="L56" t="n">
-        <v>3.55</v>
+        <v>5.19</v>
       </c>
       <c r="M56" t="n">
         <v>0.09</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,25 +4352,25 @@
         <v>6.59</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46185.55208333334</v>
+        <v>46188.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>423.9</v>
+        <v>431.35</v>
       </c>
       <c r="I57" t="n">
         <v>426.3829076029973</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>11</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K57" t="n">
-        <v>2.54</v>
+        <v>0.83</v>
       </c>
       <c r="L57" t="n">
         <v>1.93</v>
       </c>
       <c r="M57" t="n">
-        <v>1.48</v>
+        <v>1.77</v>
       </c>
       <c r="N57" t="n">
         <v>4.34</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>5.49</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46245.55208333334</v>
+        <v>46246.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>423.4</v>
+        <v>420.7</v>
       </c>
       <c r="I58" t="n">
         <v>422.1815967812889</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>57.16666666666666</v>
+        <v>58</v>
       </c>
       <c r="K58" t="n">
-        <v>-1.84</v>
+        <v>-2.47</v>
       </c>
       <c r="L58" t="n">
         <v>4.02</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>4.96</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46259.55208333334</v>
+        <v>46260.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>411</v>
+        <v>421.75</v>
       </c>
       <c r="I59" t="n">
         <v>421.2219382004836</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K59" t="n">
-        <v>2.31</v>
+        <v>-0.25</v>
       </c>
       <c r="L59" t="n">
         <v>1.43</v>
@@ -3804,7 +4511,7 @@
         <v>1.08</v>
       </c>
       <c r="N59" t="n">
-        <v>1.16</v>
+        <v>2.68</v>
       </c>
       <c r="O59" t="n">
         <v>-0.46</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>5.37</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46265.55208333334</v>
+        <v>46266.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>405</v>
+        <v>403.8</v>
       </c>
       <c r="I60" t="n">
         <v>403.9749934075018</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K60" t="n">
-        <v>-3.97</v>
+        <v>-4.26</v>
       </c>
       <c r="L60" t="n">
-        <v>4.39</v>
+        <v>4.43</v>
       </c>
       <c r="M60" t="n">
         <v>0.48</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>4.28</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46310.55208333334</v>
+        <v>46311.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>349</v>
+        <v>367.05</v>
       </c>
       <c r="I61" t="n">
         <v>364.9929644967964</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>44.16666666666666</v>
+        <v>45</v>
       </c>
       <c r="K61" t="n">
-        <v>13.57</v>
+        <v>9.1</v>
       </c>
       <c r="L61" t="n">
         <v>1.09</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -3978,6 +4721,12 @@
       <c r="Q62" t="n">
         <v>14</v>
       </c>
+      <c r="R62" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S62" t="inlineStr"/>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6080,7 +6829,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6">
@@ -6090,7 +6839,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21.2</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="7">
@@ -6100,7 +6849,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>111.2</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8">
@@ -6110,7 +6859,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -6120,7 +6869,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>41.2</v>
+        <v>41.4</v>
       </c>
     </row>
     <row r="10">
@@ -6130,7 +6879,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>55.1</v>
+        <v>55.3</v>
       </c>
     </row>
     <row r="11">
@@ -6170,7 +6919,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.14</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="15">
@@ -6180,7 +6929,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.75</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="16">
@@ -6190,7 +6939,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.52</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="17">
@@ -6200,7 +6949,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>36.58</v>
+        <v>34.7</v>
       </c>
     </row>
     <row r="18">
@@ -6210,7 +6959,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>56.7</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="19">
@@ -6220,7 +6969,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.06</v>
+        <v>4.83</v>
       </c>
     </row>
     <row r="20">
@@ -6230,7 +6979,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.66</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="21">
@@ -6240,7 +6989,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>17.92</v>
+        <v>18.76</v>
       </c>
     </row>
     <row r="22">
@@ -6250,7 +6999,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23">
@@ -6260,7 +7009,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -6270,7 +7019,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="25">
@@ -6290,7 +7039,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.39</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="27">
@@ -6300,7 +7049,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7.38</v>
+        <v>16.64</v>
       </c>
     </row>
     <row r="28">
@@ -6310,7 +7059,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29">
